--- a/outputs/15380.xlsx
+++ b/outputs/15380.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">VLOOKUP(MID(A3,FIND("_",A3)+1,FIND("_",A3,FIND("_",A3)+1)-FIND("_",A3)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A3,6,2),$D$3:$D$14,0))</f>
         <v>SEP</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -601,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A4,FIND("_",A4)+1,FIND("_",A4,FIND("_",A4)+1)-FIND("_",A4)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A4,6,2),$D$3:$D$14,0))</f>
         <v>SEP</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -616,7 +616,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A5,FIND("_",A5)+1,FIND("_",A5,FIND("_",A5)+1)-FIND("_",A5)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A5,6,2),$D$3:$D$14,0))</f>
         <v>SEP</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -631,7 +631,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A6,FIND("_",A6)+1,FIND("_",A6,FIND("_",A6)+1)-FIND("_",A6)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A6,6,2),$D$3:$D$14,0))</f>
         <v>SEP</v>
       </c>
       <c r="D6" s="6" t="s">
@@ -646,7 +646,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A7,FIND("_",A7)+1,FIND("_",A7,FIND("_",A7)+1)-FIND("_",A7)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A7,6,2),$D$3:$D$14,0))</f>
         <v>OCT</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -661,7 +661,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A8,FIND("_",A8)+1,FIND("_",A8,FIND("_",A8)+1)-FIND("_",A8)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A8,6,2),$D$3:$D$14,0))</f>
         <v>OCT</v>
       </c>
       <c r="D8" s="6" t="s">
@@ -676,7 +676,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A9,FIND("_",A9)+1,FIND("_",A9,FIND("_",A9)+1)-FIND("_",A9)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A9,6,2),$D$3:$D$14,0))</f>
         <v>OCT</v>
       </c>
       <c r="D9" s="6" t="s">
@@ -691,7 +691,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A10,FIND("_",A10)+1,FIND("_",A10,FIND("_",A10)+1)-FIND("_",A10)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A10,6,2),$D$3:$D$14,0))</f>
         <v>OCT</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -706,7 +706,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A11,FIND("_",A11)+1,FIND("_",A11,FIND("_",A11)+1)-FIND("_",A11)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A11,6,2),$D$3:$D$14,0))</f>
         <v>OCT</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -721,7 +721,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A12,FIND("_",A12)+1,FIND("_",A12,FIND("_",A12)+1)-FIND("_",A12)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A12,6,2),$D$3:$D$14,0))</f>
         <v>OCT</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -736,7 +736,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A13,FIND("_",A13)+1,FIND("_",A13,FIND("_",A13)+1)-FIND("_",A13)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A13,6,2),$D$3:$D$14,0))</f>
         <v>NOV</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -751,7 +751,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="8" t="str">
-        <f aca="false">VLOOKUP(MID(A14,FIND("_",A14)+1,FIND("_",A14,FIND("_",A14)+1)-FIND("_",A14)-1),$D$3:$E$14,2,FALSE())</f>
+        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A14,6,2),$D$3:$D$14,0))</f>
         <v>NOV</v>
       </c>
       <c r="D14" s="6" t="s">

--- a/outputs/15380.xlsx
+++ b/outputs/15380.xlsx
@@ -10,14 +10,6 @@
   <sheets>
     <sheet name="Sheet3" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="false" name="campaigns" vbProcedure="false">Sheet3!$A$3:$A$15</definedName>
-    <definedName function="false" hidden="false" name="codes" vbProcedure="false">sheet3!#ref!</definedName>
-    <definedName function="false" hidden="false" name="codes2" vbProcedure="false">Sheet3!$D$3:$D$14</definedName>
-    <definedName function="false" hidden="false" name="month" vbProcedure="false">Sheet3!$E$3:$E$14</definedName>
-    <definedName function="false" hidden="false" name="months" vbProcedure="false">#ref!</definedName>
-    <definedName function="false" hidden="false" name="Table7" vbProcedure="false">#ref!</definedName>
-  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -145,12 +137,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,70 +163,21 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -265,48 +206,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -319,73 +220,13 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFC9F0FF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Reliant Color Wheel">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -393,34 +234,34 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="333092"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EC008C"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="00AEEF"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="439539"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FFD200"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FBB034"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="EF3E42"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="AEE0E8"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="D2D2D2"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="F1F1F1"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -562,232 +403,197 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A2:E14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.71"/>
-  </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A3,6,2),$D$3:$D$14,0))</f>
+      <c r="B3" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A3,FIND("_",A3)+1,2),D3:D14,0))</f>
         <v>SEP</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A4,6,2),$D$3:$D$14,0))</f>
+      <c r="B4" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A4,FIND("_",A4)+1,2),D3:D14,0))</f>
         <v>SEP</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="0" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A5,6,2),$D$3:$D$14,0))</f>
+      <c r="B5" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A5,FIND("_",A5)+1,2),D3:D14,0))</f>
         <v>SEP</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="0" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A6,6,2),$D$3:$D$14,0))</f>
+      <c r="B6" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A6,FIND("_",A6)+1,2),D3:D14,0))</f>
         <v>SEP</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A7,6,2),$D$3:$D$14,0))</f>
+      <c r="B7" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A7,FIND("_",A7)+1,2),D3:D14,0))</f>
         <v>OCT</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A8,6,2),$D$3:$D$14,0))</f>
+      <c r="B8" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A8,FIND("_",A8)+1,2),D3:D14,0))</f>
         <v>OCT</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="0" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A9,6,2),$D$3:$D$14,0))</f>
+      <c r="B9" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A9,FIND("_",A9)+1,2),D3:D14,0))</f>
         <v>OCT</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="0" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A10,6,2),$D$3:$D$14,0))</f>
+      <c r="B10" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A10,FIND("_",A10)+1,2),D3:D14,0))</f>
         <v>OCT</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="0" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A11,6,2),$D$3:$D$14,0))</f>
+      <c r="B11" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A11,FIND("_",A11)+1,2),D3:D14,0))</f>
         <v>OCT</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A12,6,2),$D$3:$D$14,0))</f>
+      <c r="B12" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A12,FIND("_",A12)+1,2),D3:D14,0))</f>
         <v>OCT</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A13,6,2),$D$3:$D$14,0))</f>
+      <c r="B13" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A13,FIND("_",A13)+1,2),D3:D14,0))</f>
         <v>NOV</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="8" t="str">
-        <f aca="false">INDEX($E$3:$E$14,MATCH(MID(A14,6,2),$D$3:$D$14,0))</f>
+      <c r="B14" s="0" t="str">
+        <f aca="false">INDEX(E3:E14,MATCH(MID(A14,FIND("_",A14)+1,2),D3:D14,0))</f>
         <v>NOV</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="0" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="8"/>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
